--- a/dados/SURVEY_VESSELS/SURVEY_VESSELS_20260828_noite.xlsx
+++ b/dados/SURVEY_VESSELS/SURVEY_VESSELS_20260828_noite.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cefetrjbr-my.sharepoint.com/personal/12396387790_cefet-rj_br/Documents/Empresas e entrevistas/projeto logistica offshore/ofi/dados/SURVEY_VESSELS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1024" documentId="8_{2FDA8D28-226B-473E-B58F-AB3C8EEAFC38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41E38888-3889-4E62-A8E5-5F107A79379B}"/>
+  <xr:revisionPtr revIDLastSave="1051" documentId="8_{2FDA8D28-226B-473E-B58F-AB3C8EEAFC38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{038F0D07-5584-489C-B818-CA95FCD5AB68}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="2" xr2:uid="{FAEFD476-B005-4995-A964-6D919B2AA8E5}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="1" xr2:uid="{FAEFD476-B005-4995-A964-6D919B2AA8E5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="87">
   <si>
     <t>cbo</t>
   </si>
@@ -239,130 +239,70 @@
     <t>status</t>
   </si>
   <si>
-    <t>BRAM POWER</t>
-  </si>
-  <si>
     <t>Underway using Engine</t>
   </si>
   <si>
-    <t>BRAM RIO</t>
-  </si>
-  <si>
     <t>At Anchor</t>
   </si>
   <si>
-    <t>BRAM SPIRIT</t>
-  </si>
-  <si>
-    <t>BRAM TITAN</t>
-  </si>
-  <si>
     <t>Restricted Manoeuvrability</t>
   </si>
   <si>
-    <t>DELTA CARDINAL</t>
-  </si>
-  <si>
-    <t>DELTA COMMANDER</t>
-  </si>
-  <si>
-    <t>BRAM ATLAS</t>
-  </si>
-  <si>
-    <t>BRAM BAHIA</t>
-  </si>
-  <si>
-    <t>BRAM BELEM</t>
-  </si>
-  <si>
-    <t>BRAM BRASIL</t>
-  </si>
-  <si>
     <t>Moored</t>
   </si>
   <si>
-    <t>BRAM BRASILIA</t>
-  </si>
-  <si>
     <t>Stopped</t>
   </si>
   <si>
-    <t>BRAM BRAVO</t>
-  </si>
-  <si>
-    <t>BRAM BREEZE</t>
-  </si>
-  <si>
-    <t>BRAM BUCK</t>
-  </si>
-  <si>
-    <t>BRAM BUZIOS</t>
-  </si>
-  <si>
-    <t>BRAM HERO</t>
-  </si>
-  <si>
-    <t>CBO ALESSANDRA</t>
-  </si>
-  <si>
-    <t>CBO ALIANCA</t>
-  </si>
-  <si>
-    <t>CBO ANITA</t>
-  </si>
-  <si>
-    <t>CBO ARPOADOR</t>
-  </si>
-  <si>
-    <t>CBO CAMPOS</t>
-  </si>
-  <si>
-    <t>CBO CAROLINA</t>
-  </si>
-  <si>
-    <t>CBO COPACABANA</t>
-  </si>
-  <si>
-    <t>CBO ENERGY</t>
-  </si>
-  <si>
-    <t>CBO FLAMENGO</t>
-  </si>
-  <si>
-    <t>CBO IPANEMA</t>
-  </si>
-  <si>
-    <t>CBO ISABELLA</t>
-  </si>
-  <si>
-    <t>CBO ITAJAI</t>
-  </si>
-  <si>
-    <t>CBO MANOELLA</t>
-  </si>
-  <si>
-    <t>CBO OCEANA</t>
-  </si>
-  <si>
-    <t>CBO RENATA</t>
-  </si>
-  <si>
-    <t>CBO RIO</t>
-  </si>
-  <si>
     <t>Class B</t>
   </si>
   <si>
-    <t>CBO SUPPORTER</t>
-  </si>
-  <si>
-    <t>CBO VITORIA</t>
-  </si>
-  <si>
-    <t>CBO WAVE</t>
-  </si>
-  <si>
-    <t>CBO WISER</t>
+    <t>STARNAV LIBRA</t>
+  </si>
+  <si>
+    <t>STARNAV PERSEUS</t>
+  </si>
+  <si>
+    <t>STARNAV PHOENIX</t>
+  </si>
+  <si>
+    <t>STARNAV REGULUS</t>
+  </si>
+  <si>
+    <t>STARNAV TAURUS</t>
+  </si>
+  <si>
+    <t>STARNAV URSUS</t>
+  </si>
+  <si>
+    <t>STARNAV VOLANS</t>
+  </si>
+  <si>
+    <t>STARNAV AQUARIUS</t>
+  </si>
+  <si>
+    <t>STARNAV AQUILA</t>
+  </si>
+  <si>
+    <t>STARNAV CENTAURUS</t>
+  </si>
+  <si>
+    <t>STARNAV CEPHEUS</t>
+  </si>
+  <si>
+    <t>STARNAV CIRCINUS</t>
+  </si>
+  <si>
+    <t>STARNAV CYGNUS</t>
+  </si>
+  <si>
+    <t>STARNAV DELPHINUS</t>
+  </si>
+  <si>
+    <t>STARNAV DRACO</t>
+  </si>
+  <si>
+    <t>STARNAV HYDRA</t>
   </si>
 </sst>
 </file>
@@ -1100,9 +1040,7 @@
       <c r="B2" s="6">
         <v>46231.919444444444</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>86</v>
-      </c>
+      <c r="C2" s="1"/>
       <c r="D2" s="1">
         <v>-22.866510000000002</v>
       </c>
@@ -1113,7 +1051,7 @@
         <v>46230.90625</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="I2" s="1"/>
     </row>
@@ -1124,9 +1062,7 @@
       <c r="B3" s="6">
         <v>46231.919444444444</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="C3" s="1"/>
       <c r="D3" s="1">
         <v>-25.596003</v>
       </c>
@@ -1137,7 +1073,7 @@
         <v>46231.918055555558</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="I3" s="1"/>
     </row>
@@ -1148,9 +1084,7 @@
       <c r="B4" s="6">
         <v>46231.919444444444</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>88</v>
-      </c>
+      <c r="C4" s="1"/>
       <c r="D4" s="1">
         <v>-23.566326</v>
       </c>
@@ -1161,7 +1095,7 @@
         <v>46231.68472222222</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="I4" s="1"/>
     </row>
@@ -1172,9 +1106,7 @@
       <c r="B5" s="6">
         <v>46231.919444444444</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>89</v>
-      </c>
+      <c r="C5" s="1"/>
       <c r="D5" s="1">
         <v>-24.625284000000001</v>
       </c>
@@ -1185,7 +1117,7 @@
         <v>46231.918055555558</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I5" s="1"/>
     </row>
@@ -1196,9 +1128,7 @@
       <c r="B6" s="6">
         <v>46231.919444444444</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>90</v>
-      </c>
+      <c r="C6" s="1"/>
       <c r="D6" s="1">
         <v>-22.864473</v>
       </c>
@@ -1209,7 +1139,7 @@
         <v>44390.56527777778</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="I6" s="1"/>
     </row>
@@ -1220,9 +1150,7 @@
       <c r="B7" s="6">
         <v>46231.919444444444</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>91</v>
-      </c>
+      <c r="C7" s="1"/>
       <c r="D7" s="1">
         <v>-24.679089999999999</v>
       </c>
@@ -1233,7 +1161,7 @@
         <v>46231.918055555558</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I7" s="1"/>
     </row>
@@ -1244,9 +1172,7 @@
       <c r="B8" s="6">
         <v>46231.919444444444</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>92</v>
-      </c>
+      <c r="C8" s="1"/>
       <c r="D8" s="1">
         <v>-24.7652</v>
       </c>
@@ -1257,7 +1183,7 @@
         <v>46231.918055555558</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="I8" s="1"/>
     </row>
@@ -1268,9 +1194,7 @@
       <c r="B9" s="6">
         <v>46231.919444444444</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>93</v>
-      </c>
+      <c r="C9" s="1"/>
       <c r="D9" s="1">
         <v>-25.507615999999999</v>
       </c>
@@ -1281,7 +1205,7 @@
         <v>46231.918055555558</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="I9" s="1"/>
     </row>
@@ -1292,9 +1216,7 @@
       <c r="B10" s="6">
         <v>46231.919444444444</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>94</v>
-      </c>
+      <c r="C10" s="1"/>
       <c r="D10" s="1">
         <v>-21.980519999999999</v>
       </c>
@@ -1305,7 +1227,7 @@
         <v>46231.55</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="I10" s="1"/>
     </row>
@@ -1316,9 +1238,7 @@
       <c r="B11" s="6">
         <v>46231.919444444444</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>95</v>
-      </c>
+      <c r="C11" s="1"/>
       <c r="D11" s="1">
         <v>-22.841425000000001</v>
       </c>
@@ -1329,7 +1249,7 @@
         <v>46231.918055555558</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I11" s="1"/>
     </row>
@@ -1340,9 +1260,7 @@
       <c r="B12" s="6">
         <v>46231.92083333333</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>96</v>
-      </c>
+      <c r="C12" s="1"/>
       <c r="D12" s="1">
         <v>-22.844909999999999</v>
       </c>
@@ -1353,7 +1271,7 @@
         <v>46231.920138888891</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I12" s="1"/>
     </row>
@@ -1364,9 +1282,7 @@
       <c r="B13" s="6">
         <v>46231.92083333333</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>97</v>
-      </c>
+      <c r="C13" s="1"/>
       <c r="D13" s="1">
         <v>-21.985132</v>
       </c>
@@ -1377,7 +1293,7 @@
         <v>46231.879166666666</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="I13" s="1"/>
     </row>
@@ -1388,9 +1304,7 @@
       <c r="B14" s="6">
         <v>46231.92083333333</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>98</v>
-      </c>
+      <c r="C14" s="1"/>
       <c r="D14" s="1">
         <v>-25.204277000000001</v>
       </c>
@@ -1401,7 +1315,7 @@
         <v>46231.918055555558</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="I14" s="1"/>
     </row>
@@ -1412,9 +1326,7 @@
       <c r="B15" s="6">
         <v>46231.92083333333</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>99</v>
-      </c>
+      <c r="C15" s="1"/>
       <c r="D15" s="1">
         <v>-24.951736</v>
       </c>
@@ -1425,7 +1337,7 @@
         <v>46231.918749999997</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="I15" s="1"/>
     </row>
@@ -1436,9 +1348,7 @@
       <c r="B16" s="6">
         <v>46231.92083333333</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>100</v>
-      </c>
+      <c r="C16" s="1"/>
       <c r="D16" s="1">
         <v>-21.780539999999998</v>
       </c>
@@ -1449,7 +1359,7 @@
         <v>46230.955555555556</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I16" s="1"/>
     </row>
@@ -1460,9 +1370,7 @@
       <c r="B17" s="6">
         <v>46231.92083333333</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>101</v>
-      </c>
+      <c r="C17" s="1"/>
       <c r="D17" s="1">
         <v>-30.372271999999999</v>
       </c>
@@ -1473,7 +1381,7 @@
         <v>44677.811111111114</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>102</v>
+        <v>70</v>
       </c>
       <c r="I17" s="1"/>
     </row>
@@ -1484,9 +1392,7 @@
       <c r="B18" s="6">
         <v>46231.92083333333</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>103</v>
-      </c>
+      <c r="C18" s="1"/>
       <c r="D18" s="1">
         <v>-23.259981</v>
       </c>
@@ -1497,7 +1403,7 @@
         <v>46231.911111111112</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I18" s="1"/>
     </row>
@@ -1508,9 +1414,7 @@
       <c r="B19" s="6">
         <v>46231.92083333333</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="C19" s="1"/>
       <c r="D19" s="1">
         <v>-22.864526999999999</v>
       </c>
@@ -1521,7 +1425,7 @@
         <v>45839.576388888891</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="I19" s="1"/>
     </row>
@@ -1532,9 +1436,7 @@
       <c r="B20" s="6">
         <v>46231.92083333333</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>105</v>
-      </c>
+      <c r="C20" s="1"/>
       <c r="D20" s="1">
         <v>-22.998798000000001</v>
       </c>
@@ -1545,7 +1447,7 @@
         <v>46231.919444444444</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I20" s="1"/>
     </row>
@@ -1556,9 +1458,7 @@
       <c r="B21" s="6">
         <v>46231.92083333333</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>106</v>
-      </c>
+      <c r="C21" s="1"/>
       <c r="D21" s="1">
         <v>-22.868580000000001</v>
       </c>
@@ -1569,7 +1469,7 @@
         <v>46231.914583333331</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="I21" s="1"/>
     </row>
@@ -1580,9 +1480,7 @@
       <c r="B22" s="6">
         <v>46231.915972222225</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>72</v>
-      </c>
+      <c r="C22" s="1"/>
       <c r="D22" s="1">
         <v>-22.84544</v>
       </c>
@@ -1593,7 +1491,7 @@
         <v>46231.914583333331</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J22" s="1"/>
       <c r="O22" s="4"/>
@@ -1605,9 +1503,7 @@
       <c r="B23" s="6">
         <v>46231.915972222225</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>73</v>
-      </c>
+      <c r="C23" s="1"/>
       <c r="D23" s="1">
         <v>-22.845036</v>
       </c>
@@ -1618,7 +1514,7 @@
         <v>46231.910416666666</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J23" s="1"/>
     </row>
@@ -1703,9 +1599,7 @@
       <c r="B2" s="6">
         <v>46231.918055555558</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>74</v>
-      </c>
+      <c r="C2" s="1"/>
       <c r="D2" s="1">
         <v>-22.847204000000001</v>
       </c>
@@ -1716,7 +1610,7 @@
         <v>46231.911111111112</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I2" s="1"/>
     </row>
@@ -1727,9 +1621,7 @@
       <c r="B3" s="6">
         <v>46231.918055555558</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>75</v>
-      </c>
+      <c r="C3" s="1"/>
       <c r="D3" s="1">
         <v>-22.374742999999999</v>
       </c>
@@ -1740,7 +1632,7 @@
         <v>46231.84097222222</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I3" s="1"/>
     </row>
@@ -1751,9 +1643,7 @@
       <c r="B4" s="6">
         <v>46231.918055555558</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>76</v>
-      </c>
+      <c r="C4" s="1"/>
       <c r="D4" s="1">
         <v>-24.830158000000001</v>
       </c>
@@ -1764,7 +1654,7 @@
         <v>46231.914583333331</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I4" s="1"/>
     </row>
@@ -1775,9 +1665,7 @@
       <c r="B5" s="6">
         <v>46231.918055555558</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>77</v>
-      </c>
+      <c r="C5" s="1"/>
       <c r="D5" s="1">
         <v>-21.881910000000001</v>
       </c>
@@ -1788,7 +1676,7 @@
         <v>46231.915277777778</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="I5" s="1"/>
     </row>
@@ -1799,9 +1687,7 @@
       <c r="B6" s="6">
         <v>46231.918055555558</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>79</v>
-      </c>
+      <c r="C6" s="1"/>
       <c r="D6" s="1">
         <v>-22.894566999999999</v>
       </c>
@@ -1812,7 +1698,7 @@
         <v>46231.915972222225</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="I6" s="1"/>
     </row>
@@ -1823,9 +1709,7 @@
       <c r="B7" s="6">
         <v>46231.918055555558</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>81</v>
-      </c>
+      <c r="C7" s="1"/>
       <c r="D7" s="1">
         <v>-21.263290000000001</v>
       </c>
@@ -1836,7 +1720,7 @@
         <v>46231.781944444447</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="I7" s="1"/>
     </row>
@@ -1847,9 +1731,7 @@
       <c r="B8" s="6">
         <v>46231.918055555558</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>82</v>
-      </c>
+      <c r="C8" s="1"/>
       <c r="D8" s="1">
         <v>-24.754648</v>
       </c>
@@ -1860,7 +1742,7 @@
         <v>46231.911111111112</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="I8" s="1"/>
     </row>
@@ -1871,9 +1753,7 @@
       <c r="B9" s="6">
         <v>46231.918055555558</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>83</v>
-      </c>
+      <c r="C9" s="1"/>
       <c r="D9" s="1">
         <v>-22.893621</v>
       </c>
@@ -1884,7 +1764,7 @@
         <v>46231.911805555559</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="I9" s="1"/>
     </row>
@@ -1895,9 +1775,7 @@
       <c r="B10" s="6">
         <v>46231.918055555558</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>84</v>
-      </c>
+      <c r="C10" s="1"/>
       <c r="D10" s="1">
         <v>-22.925256999999998</v>
       </c>
@@ -1908,7 +1786,7 @@
         <v>46231.915277777778</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I10" s="1"/>
     </row>
@@ -1919,9 +1797,7 @@
       <c r="B11" s="6">
         <v>46231.918055555558</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="C11" s="1"/>
       <c r="D11" s="1">
         <v>-25.601783999999999</v>
       </c>
@@ -1932,7 +1808,7 @@
         <v>46231.893750000003</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="I11" s="1"/>
     </row>
@@ -1943,9 +1819,7 @@
       <c r="B12" s="6">
         <v>46231.915972222225</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>65</v>
-      </c>
+      <c r="C12" s="1"/>
       <c r="D12" s="1">
         <v>-22.428281999999999</v>
       </c>
@@ -1956,7 +1830,7 @@
         <v>46226.459027777775</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I12" s="1"/>
     </row>
@@ -1967,9 +1841,7 @@
       <c r="B13" s="6">
         <v>46231.915972222225</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>67</v>
-      </c>
+      <c r="C13" s="1"/>
       <c r="D13" s="1">
         <v>-22.84309</v>
       </c>
@@ -1980,7 +1852,7 @@
         <v>46231.913194444445</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I13" s="1"/>
     </row>
@@ -1991,9 +1863,7 @@
       <c r="B14" s="6">
         <v>46231.915972222225</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>69</v>
-      </c>
+      <c r="C14" s="1"/>
       <c r="D14" s="1">
         <v>-24.084392999999999</v>
       </c>
@@ -2004,7 +1874,7 @@
         <v>46231.913194444445</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I14" s="1"/>
     </row>
@@ -2015,9 +1885,7 @@
       <c r="B15" s="6">
         <v>46231.915972222225</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="C15" s="1"/>
       <c r="D15" s="1">
         <v>-24.742305999999999</v>
       </c>
@@ -2028,7 +1896,7 @@
         <v>46231.869444444441</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="I15" s="1"/>
     </row>
@@ -2100,130 +1968,262 @@
       <c r="A2" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="6"/>
+      <c r="B2" s="6">
+        <v>46231.925000000003</v>
+      </c>
       <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="6"/>
-      <c r="H2" s="1"/>
+      <c r="D2" s="1">
+        <v>-22.891062000000002</v>
+      </c>
+      <c r="E2" s="1">
+        <v>-43.213844000000002</v>
+      </c>
+      <c r="F2" s="6">
+        <v>46231.92083333333</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="I2" s="1"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="6"/>
-      <c r="H3" s="1"/>
+      <c r="B3" s="6">
+        <v>46231.925000000003</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D3" s="1">
+        <v>-24.725058000000001</v>
+      </c>
+      <c r="E3" s="1">
+        <v>-42.417465</v>
+      </c>
+      <c r="F3" s="6">
+        <v>46231.918055555558</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="I3" s="1"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="6"/>
-      <c r="H4" s="1"/>
+      <c r="B4" s="6">
+        <v>46231.925000000003</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D4" s="1">
+        <v>-22.464659000000001</v>
+      </c>
+      <c r="E4" s="1">
+        <v>-40.058365000000002</v>
+      </c>
+      <c r="F4" s="6">
+        <v>46231.851388888892</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="I4" s="1"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="6"/>
-      <c r="H5" s="1"/>
+      <c r="B5" s="6">
+        <v>46231.925000000003</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D5" s="1">
+        <v>-22.838804</v>
+      </c>
+      <c r="E5" s="1">
+        <v>-43.141227999999998</v>
+      </c>
+      <c r="F5" s="6">
+        <v>46231.920138888891</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="I5" s="1"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>52</v>
       </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="6"/>
-      <c r="H6" s="1"/>
+      <c r="B6" s="6">
+        <v>46231.925000000003</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D6" s="1">
+        <v>-21.854692</v>
+      </c>
+      <c r="E6" s="1">
+        <v>-40.961243000000003</v>
+      </c>
+      <c r="F6" s="6">
+        <v>46231.92083333333</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="I6" s="1"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>54</v>
       </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="6"/>
-      <c r="H7" s="1"/>
+      <c r="B7" s="6">
+        <v>46231.925000000003</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D7" s="1">
+        <v>-21.855045</v>
+      </c>
+      <c r="E7" s="1">
+        <v>-41.008755000000001</v>
+      </c>
+      <c r="F7" s="6">
+        <v>46231.920138888891</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="I7" s="1"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="6"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="H8" s="1"/>
+      <c r="B8" s="6">
+        <v>46231.925000000003</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D8" s="1">
+        <v>-21.973223000000001</v>
+      </c>
+      <c r="E8" s="1">
+        <v>-40.256976999999999</v>
+      </c>
+      <c r="F8" s="6">
+        <v>46231.897222222222</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="I8" s="1"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>55</v>
       </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="6"/>
-      <c r="H9" s="1"/>
+      <c r="B9" s="6">
+        <v>46231.925000000003</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D9" s="1">
+        <v>-22.673666000000001</v>
+      </c>
+      <c r="E9" s="1">
+        <v>-40.546340999999998</v>
+      </c>
+      <c r="F9" s="6">
+        <v>46231.757638888892</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="I9" s="1"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="6"/>
-      <c r="H10" s="1"/>
+      <c r="B10" s="6">
+        <v>46231.925000000003</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D10" s="1">
+        <v>-22.541021000000001</v>
+      </c>
+      <c r="E10" s="1">
+        <v>-40.086253999999997</v>
+      </c>
+      <c r="F10" s="6">
+        <v>46231.830555555556</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="I10" s="1"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>56</v>
       </c>
-      <c r="B11" s="6"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="6"/>
-      <c r="H11" s="1"/>
+      <c r="B11" s="6">
+        <v>46231.925000000003</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D11" s="1">
+        <v>-21.953928000000001</v>
+      </c>
+      <c r="E11" s="1">
+        <v>-39.793807999999999</v>
+      </c>
+      <c r="F11" s="6">
+        <v>46231.910416666666</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="I11" s="1"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="6"/>
-      <c r="H12" s="1"/>
+      <c r="B12" s="6">
+        <v>46231.92291666667</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D12" s="1">
+        <v>-22.856476000000001</v>
+      </c>
+      <c r="E12" s="1">
+        <v>-43.161876999999997</v>
+      </c>
+      <c r="F12" s="6">
+        <v>46231.918749999997</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="I12" s="1"/>
       <c r="N12" s="1"/>
     </row>
@@ -2231,11 +2231,24 @@
       <c r="A13" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="6"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="6"/>
-      <c r="H13" s="1"/>
+      <c r="B13" s="6">
+        <v>46231.92291666667</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D13" s="1">
+        <v>-21.863303999999999</v>
+      </c>
+      <c r="E13" s="1">
+        <v>-41.017288000000001</v>
+      </c>
+      <c r="F13" s="6">
+        <v>46231.92291666667</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="I13" s="1"/>
       <c r="N13" s="1"/>
     </row>
@@ -2243,55 +2256,120 @@
       <c r="A14" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="6"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="6"/>
-      <c r="H14" s="1"/>
+      <c r="B14" s="6">
+        <v>46231.92291666667</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D14" s="1">
+        <v>-25.799709</v>
+      </c>
+      <c r="E14" s="1">
+        <v>-43.263660000000002</v>
+      </c>
+      <c r="F14" s="6">
+        <v>46231.921527777777</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="I14" s="1"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="6"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="6"/>
-      <c r="H15" s="1"/>
+      <c r="B15" s="6">
+        <v>46231.92291666667</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D15" s="1">
+        <v>-22.860838000000001</v>
+      </c>
+      <c r="E15" s="1">
+        <v>-43.167628999999998</v>
+      </c>
+      <c r="F15" s="6">
+        <v>46231.913888888892</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="I15" s="1"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="6"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="6"/>
-      <c r="H16" s="1"/>
+      <c r="B16" s="6">
+        <v>46231.92291666667</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D16" s="1">
+        <v>-22.853504000000001</v>
+      </c>
+      <c r="E16" s="1">
+        <v>-43.140735999999997</v>
+      </c>
+      <c r="F16" s="6">
+        <v>46231.916666666664</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="I16" s="1"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="6"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="6"/>
-      <c r="H17" s="1"/>
+      <c r="B17" s="6">
+        <v>46231.92291666667</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D17" s="1">
+        <v>-26.856745</v>
+      </c>
+      <c r="E17" s="1">
+        <v>-48.721401</v>
+      </c>
+      <c r="F17" s="6">
+        <v>46120.325694444444</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="I17" s="1"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>53</v>
       </c>
-      <c r="B18" s="6"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="6"/>
-      <c r="H18" s="1"/>
+      <c r="B18" s="6">
+        <v>46231.92291666667</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D18" s="1">
+        <v>-24.542100999999999</v>
+      </c>
+      <c r="E18" s="1">
+        <v>-42.131641000000002</v>
+      </c>
+      <c r="F18" s="6">
+        <v>46231.914583333331</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="I18" s="1"/>
     </row>
   </sheetData>
